--- a/ttl_long/AdHoc_Net_2.xlsx
+++ b/ttl_long/AdHoc_Net_2.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>250</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>277</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>449</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>169</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>367</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>322</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>460</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>609</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>491</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>599</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>706</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>176</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>649</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>650</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>871</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>885</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>318</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>821</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>1027</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>901</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>999</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1132</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1073</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1145</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1172</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1224</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>329</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1232</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1416</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>244</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1334</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1384</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1426</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1606</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1543</t>
         </is>
       </c>
     </row>
@@ -1055,80 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1495</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1489</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1512</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1665</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1565</t>
+          <t>405</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1130,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1152,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1242,7 +1174,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1264,7 +1196,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1218,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1240,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1330,7 +1262,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1284,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,7 +1306,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1396,7 +1328,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1350,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1372,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1479,12 +1411,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1501,12 +1433,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1455,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1545,12 +1477,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1504,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1589,12 +1521,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,12 +1543,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1633,7 +1565,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1655,7 +1587,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1677,12 +1609,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,12 +1631,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1653,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1765,7 +1697,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1787,12 +1719,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1746,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,12 +1763,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,12 +1785,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1807,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1829,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1851,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1946,7 +1878,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1895,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2012,7 +1944,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,12 +1961,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +1983,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2005,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2027,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2049,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2071,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2093,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2115,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2137,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2159,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2181,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2203,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2225,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2247,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2269,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2291,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2313,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2335,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2357,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2379,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2474,7 +2406,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2513,12 +2445,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2467,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2562,7 +2494,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2511,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2533,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2555,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,7 +2577,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2667,12 +2599,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2621,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2643,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2665,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2687,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2709,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2731,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2753,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2775,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2797,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2819,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2841,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2863,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2885,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2907,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2929,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +2951,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,7 +2973,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3063,12 +2995,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3017,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3039,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3061,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3083,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3105,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3127,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3149,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3171,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3193,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,7 +3215,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3305,12 +3237,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3259,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3281,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3303,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3325,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3407,424 +3339,6 @@
         </is>
       </c>
       <c r="D103" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3863,7 +3377,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3873,7 +3387,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -3899,7 +3413,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_2.xlsx
+++ b/ttl_long/AdHoc_Net_2.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>260</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>215</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>344</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>246</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>303</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>397</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>532</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>544</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>516</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>567</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>595</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>289</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>587</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>783</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>710</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>734</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>914</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>783</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>901</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>930</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1014</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>331</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1119</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1129</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>289</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1155</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1273</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1196</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1227</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1429</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>264</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1386</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1328</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,80 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>375</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>405</t>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>307</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1130,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1152,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1174,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1196,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1218,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1257,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1284,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1306,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1323,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1350,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1372,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1389,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1416,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1433,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1482,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1504,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1521,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1548,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1565,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1587,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1614,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1631,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1658,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1680,7 +1748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1697,7 +1765,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1724,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1763,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1790,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1812,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1834,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1856,7 +1924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1878,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1922,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1944,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1966,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1983,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2010,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2032,7 +2100,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2054,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2098,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2120,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2137,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2164,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2181,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2203,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2230,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2252,7 +2320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2296,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2335,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2362,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2406,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2450,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2472,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2494,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2511,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2538,7 +2606,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2560,7 +2628,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2577,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2604,7 +2672,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2626,7 +2694,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2643,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2665,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2687,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2709,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2731,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2753,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2775,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2819,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2841,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2868,7 +2936,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2890,7 +2958,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2907,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2934,7 +3002,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2956,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2973,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3017,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3039,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3083,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3110,7 +3178,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3127,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3149,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3176,7 +3244,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3193,7 +3261,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3215,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3237,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3259,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3281,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3303,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3325,20 +3393,372 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3377,7 +3797,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3387,7 +3807,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -3407,7 +3827,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_2.xlsx
+++ b/ttl_long/AdHoc_Net_2.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>332</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>391</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>354</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>444</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>118</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>444</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>309</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>560</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>692</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>332</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>648</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>678</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>767</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>784</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>821</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>185</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>805</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>885</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>937</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>954</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1158</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1199</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1078</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1226</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1294</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1276</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1366</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1312</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1325</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1498</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1527</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1515</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1651</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>190</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>1530</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3627,138 +3627,6 @@
         </is>
       </c>
       <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3797,7 +3665,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
